--- a/plm python control/wrappers/multibeam parameters/multibeam diamond/multiBeam_innerCW_outerCCW_normalPhase_A_040_B_100.xlsx
+++ b/plm python control/wrappers/multibeam parameters/multibeam diamond/multiBeam_innerCW_outerCCW_normalPhase_A_040_B_100.xlsx
@@ -512,7 +512,7 @@
         <v>8</v>
       </c>
       <c r="D11">
-        <v>1.076901077801928</v>
+        <v>1.163251963712884</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -652,7 +652,7 @@
         <v>8</v>
       </c>
       <c r="D22">
-        <v>0.9542058541740658</v>
+        <v>0.9845733764160133</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -792,7 +792,7 @@
         <v>8</v>
       </c>
       <c r="D33">
-        <v>0.8596981108972922</v>
+        <v>0.8958762313135574</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -932,7 +932,7 @@
         <v>8</v>
       </c>
       <c r="D44">
-        <v>1.00706779492958</v>
+        <v>0.9929129969454336</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1072,7 +1072,7 @@
         <v>8</v>
       </c>
       <c r="D55">
-        <v>0.8000766280078387</v>
+        <v>0.8116636731822621</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1212,7 +1212,7 @@
         <v>8</v>
       </c>
       <c r="D66">
-        <v>0.7613164793056466</v>
+        <v>0.7464301203421082</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1352,7 +1352,7 @@
         <v>8</v>
       </c>
       <c r="D77">
-        <v>1.176327153103565</v>
+        <v>1.20265742720488</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1492,7 +1492,7 @@
         <v>8</v>
       </c>
       <c r="D88">
-        <v>0.8493345689586644</v>
+        <v>0.85595506564045</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -1632,7 +1632,7 @@
         <v>8</v>
       </c>
       <c r="D99">
-        <v>0.7519790145598976</v>
+        <v>0.7232866397331975</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -1772,7 +1772,7 @@
         <v>8</v>
       </c>
       <c r="D110">
-        <v>1.076962886884533</v>
+        <v>1.143816190773048</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -1912,7 +1912,7 @@
         <v>8</v>
       </c>
       <c r="D121">
-        <v>0.9518170958731089</v>
+        <v>0.9173587496461394</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2052,7 +2052,7 @@
         <v>8</v>
       </c>
       <c r="D132">
-        <v>0.8534975024145471</v>
+        <v>0.8192254497074715</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2178,7 +2178,7 @@
         <v>7</v>
       </c>
       <c r="D142">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -2192,7 +2192,7 @@
         <v>8</v>
       </c>
       <c r="D143">
-        <v>0.8264276674516406</v>
+        <v>0.8271484970525158</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -2332,7 +2332,7 @@
         <v>8</v>
       </c>
       <c r="D154">
-        <v>0.871718881589572</v>
+        <v>0.7741764888153944</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -2472,7 +2472,7 @@
         <v>8</v>
       </c>
       <c r="D165">
-        <v>0.8603710739283469</v>
+        <v>0.8146651860426058</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -2612,7 +2612,7 @@
         <v>8</v>
       </c>
       <c r="D176">
-        <v>1.203310800118084</v>
+        <v>1.12237181892834</v>
       </c>
     </row>
   </sheetData>

--- a/plm python control/wrappers/multibeam parameters/multibeam diamond/multiBeam_innerCW_outerCCW_normalPhase_A_040_B_100.xlsx
+++ b/plm python control/wrappers/multibeam parameters/multibeam diamond/multiBeam_innerCW_outerCCW_normalPhase_A_040_B_100.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PLM\plm python control\wrappers\multibeam parameters\multibeam diamond\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FB68138-6770-4FCF-87E3-EF12736C1182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="3330" yWindow="1950" windowWidth="5925" windowHeight="11505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -19,19 +25,19 @@
     <t>Beam A</t>
   </si>
   <si>
-    <t>Beam B</t>
-  </si>
-  <si>
-    <t>Beam</t>
-  </si>
-  <si>
     <t>Grating period X (plm pix)</t>
   </si>
   <si>
     <t>Grating period Y (plm pix)</t>
   </si>
   <si>
+    <t>Beam B</t>
+  </si>
+  <si>
     <t>Relative phase (%)</t>
+  </si>
+  <si>
+    <t>Beam</t>
   </si>
   <si>
     <t>Global phase (%)</t>
@@ -46,8 +52,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -84,6 +90,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -371,11 +385,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:D176"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -383,13 +397,13 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>13.14222222222222</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -397,41 +411,41 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>11.73055555555555</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>11.730555555555551</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4">
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>85.559</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>85.558999999999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D5">
         <v>11.5845</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -439,29 +453,29 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6">
         <v>46.4</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B7">
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B8">
         <v>4</v>
@@ -473,7 +487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -487,9 +501,9 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B10">
         <v>4</v>
@@ -501,9 +515,9 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B11">
         <v>4</v>
@@ -512,10 +526,10 @@
         <v>8</v>
       </c>
       <c r="D11">
-        <v>1.163251963712884</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>0</v>
       </c>
@@ -523,13 +537,13 @@
         <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D13">
-        <v>12.69972451790634</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+        <v>11.770625798212009</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -537,41 +551,41 @@
         <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D14">
-        <v>11.32614018977655</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+        <v>12.01596424010217</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B15">
         <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D15">
-        <v>69.572</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+        <v>48.572000000000003</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B16">
         <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16">
-        <v>11.1845</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
+        <v>11.864000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>0</v>
       </c>
@@ -579,29 +593,29 @@
         <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D17">
-        <v>46.6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+        <v>42.8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B18">
         <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B19">
         <v>10</v>
@@ -613,7 +627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>0</v>
       </c>
@@ -624,12 +638,12 @@
         <v>7</v>
       </c>
       <c r="D20">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B21">
         <v>10</v>
@@ -638,12 +652,12 @@
         <v>7</v>
       </c>
       <c r="D21">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B22">
         <v>10</v>
@@ -652,10 +666,10 @@
         <v>8</v>
       </c>
       <c r="D22">
-        <v>0.9845733764160133</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>0</v>
       </c>
@@ -663,13 +677,13 @@
         <v>12</v>
       </c>
       <c r="C24" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>12.63108778069408</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
+        <v>11.1033138401559</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>0</v>
       </c>
@@ -677,41 +691,41 @@
         <v>12</v>
       </c>
       <c r="C25" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D25">
-        <v>12.10411198600175</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
+        <v>11.1842105263158</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B26">
         <v>12</v>
       </c>
       <c r="C26" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D26">
-        <v>67.572</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
+        <v>38.851999999999997</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B27">
         <v>12</v>
       </c>
       <c r="C27" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D27">
-        <v>11.95</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
+        <v>11.044499999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>0</v>
       </c>
@@ -719,29 +733,29 @@
         <v>12</v>
       </c>
       <c r="C28" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D28">
-        <v>46.6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B29">
         <v>12</v>
       </c>
       <c r="C29" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B30">
         <v>12</v>
@@ -753,7 +767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>0</v>
       </c>
@@ -767,9 +781,9 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B32">
         <v>12</v>
@@ -781,9 +795,9 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B33">
         <v>12</v>
@@ -792,10 +806,10 @@
         <v>8</v>
       </c>
       <c r="D33">
-        <v>0.8958762313135574</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>0</v>
       </c>
@@ -803,13 +817,13 @@
         <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D35">
-        <v>12.30681003584229</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
+        <v>11.4966532797858</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>0</v>
       </c>
@@ -817,41 +831,41 @@
         <v>16</v>
       </c>
       <c r="C36" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D36">
-        <v>10.92712066905615</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
+        <v>10.8762829094154</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B37">
         <v>16</v>
       </c>
       <c r="C37" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D37">
-        <v>59.212</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
+        <v>44.171999999999997</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B38">
         <v>16</v>
       </c>
       <c r="C38" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D38">
-        <v>10.7975</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
+        <v>10.741</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>0</v>
       </c>
@@ -859,29 +873,29 @@
         <v>16</v>
       </c>
       <c r="C39" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D39">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
+        <v>42.2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B40">
         <v>16</v>
       </c>
       <c r="C40" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D40">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B41">
         <v>16</v>
@@ -893,7 +907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>0</v>
       </c>
@@ -907,9 +921,9 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B43">
         <v>16</v>
@@ -921,9 +935,9 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B44">
         <v>16</v>
@@ -932,10 +946,10 @@
         <v>8</v>
       </c>
       <c r="D44">
-        <v>0.9929129969454336</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>0</v>
       </c>
@@ -943,13 +957,13 @@
         <v>18</v>
       </c>
       <c r="C46" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D46">
         <v>12.2357850808555</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>0</v>
       </c>
@@ -957,41 +971,41 @@
         <v>18</v>
       </c>
       <c r="C47" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D47">
-        <v>11.64058424621805</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
+        <v>11.640584246218051</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B48">
         <v>18</v>
       </c>
       <c r="C48" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D48">
-        <v>57.612</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
+        <v>57.612000000000002</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B49">
         <v>18</v>
       </c>
       <c r="C49" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D49">
-        <v>11.4995</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
+        <v>11.499499999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>0</v>
       </c>
@@ -999,29 +1013,29 @@
         <v>18</v>
       </c>
       <c r="C50" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D50">
         <v>42.8</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B51">
         <v>18</v>
       </c>
       <c r="C51" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B52">
         <v>18</v>
@@ -1033,7 +1047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>0</v>
       </c>
@@ -1047,9 +1061,9 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B54">
         <v>18</v>
@@ -1061,9 +1075,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B55">
         <v>18</v>
@@ -1072,10 +1086,10 @@
         <v>8</v>
       </c>
       <c r="D55">
-        <v>0.8116636731822621</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
+        <v>0.81876215981357381</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>0</v>
       </c>
@@ -1083,13 +1097,13 @@
         <v>20</v>
       </c>
       <c r="C57" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D57">
-        <v>12.15440329218107</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
+        <v>11.3696498054475</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>0</v>
       </c>
@@ -1097,41 +1111,41 @@
         <v>20</v>
       </c>
       <c r="C58" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D58">
-        <v>12.48312757201646</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
+        <v>12.4218187058654</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B59">
         <v>20</v>
       </c>
       <c r="C59" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D59">
-        <v>55.852</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
+        <v>42.451999999999998</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B60">
         <v>20</v>
       </c>
       <c r="C60" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D60">
-        <v>12.3195</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
+        <v>12.256</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>0</v>
       </c>
@@ -1139,29 +1153,29 @@
         <v>20</v>
       </c>
       <c r="C61" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D61">
-        <v>44.6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
+        <v>39.6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B62">
         <v>20</v>
       </c>
       <c r="C62" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B63">
         <v>20</v>
@@ -1173,7 +1187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>0</v>
       </c>
@@ -1187,9 +1201,9 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="65" spans="1:4">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B65">
         <v>20</v>
@@ -1201,9 +1215,9 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="66" spans="1:4">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B66">
         <v>20</v>
@@ -1212,10 +1226,10 @@
         <v>8</v>
       </c>
       <c r="D66">
-        <v>0.7464301203421082</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>0</v>
       </c>
@@ -1223,13 +1237,13 @@
         <v>22</v>
       </c>
       <c r="C68" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D68">
-        <v>11.92547834843907</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
+        <v>12.69972451790634</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>0</v>
       </c>
@@ -1237,41 +1251,41 @@
         <v>22</v>
       </c>
       <c r="C69" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D69">
-        <v>10.56394763343404</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
+        <v>11.326140189776551</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B70">
         <v>22</v>
       </c>
       <c r="C70" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D70">
-        <v>51.38</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
+        <v>69.572000000000003</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B71">
         <v>22</v>
       </c>
       <c r="C71" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D71">
-        <v>10.4405</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4">
+        <v>11.1845</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>0</v>
       </c>
@@ -1279,29 +1293,29 @@
         <v>22</v>
       </c>
       <c r="C72" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D72">
-        <v>36.4</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4">
+        <v>46.6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B73">
         <v>22</v>
       </c>
       <c r="C73" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D73">
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:4">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B74">
         <v>22</v>
@@ -1313,7 +1327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:4">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>0</v>
       </c>
@@ -1327,9 +1341,9 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="76" spans="1:4">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B76">
         <v>22</v>
@@ -1341,9 +1355,9 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="77" spans="1:4">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B77">
         <v>22</v>
@@ -1352,10 +1366,10 @@
         <v>8</v>
       </c>
       <c r="D77">
-        <v>1.20265742720488</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>0</v>
       </c>
@@ -1363,13 +1377,13 @@
         <v>24</v>
       </c>
       <c r="C79" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D79">
-        <v>11.8576306803257</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4">
+        <v>12.154403292181071</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>0</v>
       </c>
@@ -1377,41 +1391,41 @@
         <v>24</v>
       </c>
       <c r="C80" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D80">
-        <v>11.24573154715</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4">
+        <v>12.483127572016461</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B81">
         <v>24</v>
       </c>
       <c r="C81" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D81">
-        <v>50.212</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4">
+        <v>55.851999999999997</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B82">
         <v>24</v>
       </c>
       <c r="C82" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D82">
-        <v>11.11</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4">
+        <v>12.3195</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>0</v>
       </c>
@@ -1419,29 +1433,29 @@
         <v>24</v>
       </c>
       <c r="C83" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D83">
-        <v>37.2</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4">
+        <v>44.6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B84">
         <v>24</v>
       </c>
       <c r="C84" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D84">
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:4">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B85">
         <v>24</v>
@@ -1453,7 +1467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:4">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>0</v>
       </c>
@@ -1464,12 +1478,12 @@
         <v>7</v>
       </c>
       <c r="D86">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B87">
         <v>24</v>
@@ -1478,12 +1492,12 @@
         <v>7</v>
       </c>
       <c r="D87">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B88">
         <v>24</v>
@@ -1492,10 +1506,10 @@
         <v>8</v>
       </c>
       <c r="D88">
-        <v>0.85595506564045</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4">
+        <v>0.73684223482664546</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>0</v>
       </c>
@@ -1503,13 +1517,13 @@
         <v>26</v>
       </c>
       <c r="C90" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D90">
-        <v>11.77062579821201</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4">
+        <v>11.8576306803257</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>0</v>
       </c>
@@ -1517,41 +1531,41 @@
         <v>26</v>
       </c>
       <c r="C91" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D91">
-        <v>12.01596424010217</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4">
+        <v>11.245731547149999</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B92">
         <v>26</v>
       </c>
       <c r="C92" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D92">
-        <v>48.572</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4">
+        <v>50.212000000000003</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B93">
         <v>26</v>
       </c>
       <c r="C93" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D93">
-        <v>11.864</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>0</v>
       </c>
@@ -1559,29 +1573,29 @@
         <v>26</v>
       </c>
       <c r="C94" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D94">
-        <v>42.8</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4">
+        <v>37.200000000000003</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B95">
         <v>26</v>
       </c>
       <c r="C95" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D95">
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:4">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B96">
         <v>26</v>
@@ -1593,7 +1607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>0</v>
       </c>
@@ -1607,9 +1621,9 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B98">
         <v>26</v>
@@ -1621,9 +1635,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B99">
         <v>26</v>
@@ -1632,10 +1646,10 @@
         <v>8</v>
       </c>
       <c r="D99">
-        <v>0.7232866397331975</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4">
+        <v>0.92039259768939907</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>0</v>
       </c>
@@ -1643,13 +1657,13 @@
         <v>28</v>
       </c>
       <c r="C101" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D101">
-        <v>11.7109144542773</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4">
+        <v>12.631087780694079</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>0</v>
       </c>
@@ -1657,41 +1671,41 @@
         <v>28</v>
       </c>
       <c r="C102" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D102">
-        <v>12.9203539823009</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4">
+        <v>12.104111986001749</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B103">
         <v>28</v>
       </c>
       <c r="C103" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D103">
-        <v>47.472</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4">
+        <v>67.572000000000003</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B104">
         <v>28</v>
       </c>
       <c r="C104" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D104">
-        <v>12.7325</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4">
+        <v>11.95</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>0</v>
       </c>
@@ -1699,29 +1713,29 @@
         <v>28</v>
       </c>
       <c r="C105" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D105">
-        <v>51.4</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4">
+        <v>46.6</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B106">
         <v>28</v>
       </c>
       <c r="C106" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D106">
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B107">
         <v>28</v>
@@ -1733,7 +1747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>0</v>
       </c>
@@ -1747,9 +1761,9 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B109">
         <v>28</v>
@@ -1761,9 +1775,9 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="110" spans="1:4">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B110">
         <v>28</v>
@@ -1772,10 +1786,10 @@
         <v>8</v>
       </c>
       <c r="D110">
-        <v>1.143816190773048</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>0</v>
       </c>
@@ -1783,13 +1797,13 @@
         <v>30</v>
       </c>
       <c r="C112" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D112">
-        <v>11.4966532797858</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4">
+        <v>11.92547834843907</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>0</v>
       </c>
@@ -1797,41 +1811,41 @@
         <v>30</v>
       </c>
       <c r="C113" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D113">
-        <v>10.8762829094154</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4">
+        <v>10.56394763343404</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B114">
         <v>30</v>
       </c>
       <c r="C114" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D114">
-        <v>44.172</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4">
+        <v>51.38</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B115">
         <v>30</v>
       </c>
       <c r="C115" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D115">
-        <v>10.741</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4">
+        <v>10.4405</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>0</v>
       </c>
@@ -1839,29 +1853,29 @@
         <v>30</v>
       </c>
       <c r="C116" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D116">
-        <v>42.2</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4">
+        <v>36.4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B117">
         <v>30</v>
       </c>
       <c r="C117" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D117">
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:4">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B118">
         <v>30</v>
@@ -1873,7 +1887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:4">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>0</v>
       </c>
@@ -1887,9 +1901,9 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="120" spans="1:4">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B120">
         <v>30</v>
@@ -1901,9 +1915,9 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="121" spans="1:4">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B121">
         <v>30</v>
@@ -1912,10 +1926,10 @@
         <v>8</v>
       </c>
       <c r="D121">
-        <v>0.9173587496461394</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4">
+        <v>1.2708451942356651</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>0</v>
       </c>
@@ -1923,13 +1937,13 @@
         <v>32</v>
       </c>
       <c r="C123" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D123">
-        <v>11.4428341384863</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4">
+        <v>12.30681003584229</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>0</v>
       </c>
@@ -1937,41 +1951,41 @@
         <v>32</v>
       </c>
       <c r="C124" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D124">
-        <v>11.5901771336554</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4">
+        <v>10.92712066905615</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B125">
         <v>32</v>
       </c>
       <c r="C125" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D125">
-        <v>43.392</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4">
+        <v>59.212000000000003</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B126">
         <v>32</v>
       </c>
       <c r="C126" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D126">
-        <v>11.444</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4">
+        <v>10.797499999999999</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>0</v>
       </c>
@@ -1979,29 +1993,29 @@
         <v>32</v>
       </c>
       <c r="C127" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D127">
         <v>41</v>
       </c>
     </row>
-    <row r="128" spans="1:4">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B128">
         <v>32</v>
       </c>
       <c r="C128" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D128">
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:4">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B129">
         <v>32</v>
@@ -2013,7 +2027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:4">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>0</v>
       </c>
@@ -2024,12 +2038,12 @@
         <v>7</v>
       </c>
       <c r="D130">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B131">
         <v>32</v>
@@ -2038,12 +2052,12 @@
         <v>7</v>
       </c>
       <c r="D131">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B132">
         <v>32</v>
@@ -2052,10 +2066,10 @@
         <v>8</v>
       </c>
       <c r="D132">
-        <v>0.8192254497074715</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4">
+        <v>0.94662806543635647</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>0</v>
       </c>
@@ -2063,13 +2077,13 @@
         <v>34</v>
       </c>
       <c r="C134" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D134">
-        <v>11.3696498054475</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4">
+        <v>10.737638161721931</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>0</v>
       </c>
@@ -2077,41 +2091,41 @@
         <v>34</v>
       </c>
       <c r="C135" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D135">
-        <v>12.4218187058654</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4">
+        <v>11.51832460732984</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B136">
         <v>34</v>
       </c>
       <c r="C136" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D136">
-        <v>42.452</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4">
+        <v>34.752000000000002</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B137">
         <v>34</v>
       </c>
       <c r="C137" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D137">
-        <v>12.256</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4">
+        <v>11.38</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>0</v>
       </c>
@@ -2119,29 +2133,29 @@
         <v>34</v>
       </c>
       <c r="C138" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D138">
-        <v>39.6</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B139">
         <v>34</v>
       </c>
       <c r="C139" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D139">
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:4">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B140">
         <v>34</v>
@@ -2153,7 +2167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:4">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>0</v>
       </c>
@@ -2167,9 +2181,9 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="142" spans="1:4">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B142">
         <v>34</v>
@@ -2181,9 +2195,9 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="143" spans="1:4">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B143">
         <v>34</v>
@@ -2192,10 +2206,10 @@
         <v>8</v>
       </c>
       <c r="D143">
-        <v>0.8271484970525158</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4">
+        <v>1.5743101960298529</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>0</v>
       </c>
@@ -2203,13 +2217,13 @@
         <v>38</v>
       </c>
       <c r="C145" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D145">
-        <v>11.1033138401559</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4">
+        <v>11.442834138486299</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>0</v>
       </c>
@@ -2217,41 +2231,41 @@
         <v>38</v>
       </c>
       <c r="C146" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D146">
-        <v>11.1842105263158</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4">
+        <v>11.5901771336554</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B147">
         <v>38</v>
       </c>
       <c r="C147" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D147">
-        <v>38.852</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4">
+        <v>43.392000000000003</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B148">
         <v>38</v>
       </c>
       <c r="C148" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D148">
-        <v>11.0445</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4">
+        <v>11.444000000000001</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>0</v>
       </c>
@@ -2259,29 +2273,29 @@
         <v>38</v>
       </c>
       <c r="C149" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D149">
-        <v>42.2</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B150">
         <v>38</v>
       </c>
       <c r="C150" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D150">
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:4">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B151">
         <v>38</v>
@@ -2293,7 +2307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:4">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>0</v>
       </c>
@@ -2304,12 +2318,12 @@
         <v>7</v>
       </c>
       <c r="D152">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B153">
         <v>38</v>
@@ -2318,12 +2332,12 @@
         <v>7</v>
       </c>
       <c r="D153">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B154">
         <v>38</v>
@@ -2332,10 +2346,10 @@
         <v>8</v>
       </c>
       <c r="D154">
-        <v>0.7741764888153944</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4">
+        <v>0.96439624229833343</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>0</v>
       </c>
@@ -2343,13 +2357,13 @@
         <v>40</v>
       </c>
       <c r="C156" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D156">
         <v>11.041366041366</v>
       </c>
     </row>
-    <row r="157" spans="1:4">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>0</v>
       </c>
@@ -2357,41 +2371,41 @@
         <v>40</v>
       </c>
       <c r="C157" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D157">
         <v>11.9450456950457</v>
       </c>
     </row>
-    <row r="158" spans="1:4">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B158">
         <v>40</v>
       </c>
       <c r="C158" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D158">
-        <v>38.11199999999999</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4">
+        <v>38.111999999999988</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B159">
         <v>40</v>
       </c>
       <c r="C159" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D159">
-        <v>11.806</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4">
+        <v>11.805999999999999</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>0</v>
       </c>
@@ -2399,29 +2413,29 @@
         <v>40</v>
       </c>
       <c r="C160" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D160">
-        <v>37.2</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4">
+        <v>37.200000000000003</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B161">
         <v>40</v>
       </c>
       <c r="C161" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D161">
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:4">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B162">
         <v>40</v>
@@ -2433,7 +2447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:4">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>0</v>
       </c>
@@ -2447,9 +2461,9 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="164" spans="1:4">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B164">
         <v>40</v>
@@ -2461,9 +2475,9 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="165" spans="1:4">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B165">
         <v>40</v>
@@ -2472,10 +2486,10 @@
         <v>8</v>
       </c>
       <c r="D165">
-        <v>0.8146651860426058</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>0</v>
       </c>
@@ -2483,13 +2497,13 @@
         <v>46</v>
       </c>
       <c r="C167" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D167">
-        <v>10.73763816172193</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4">
+        <v>11.710914454277299</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>0</v>
       </c>
@@ -2497,41 +2511,41 @@
         <v>46</v>
       </c>
       <c r="C168" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D168">
-        <v>11.51832460732984</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4">
+        <v>12.920353982300901</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B169">
         <v>46</v>
       </c>
       <c r="C169" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D169">
-        <v>34.752</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4">
+        <v>47.472000000000001</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B170">
         <v>46</v>
       </c>
       <c r="C170" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D170">
-        <v>11.38</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4">
+        <v>12.7325</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>0</v>
       </c>
@@ -2539,29 +2553,29 @@
         <v>46</v>
       </c>
       <c r="C171" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D171">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4">
+        <v>51.4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B172">
         <v>46</v>
       </c>
       <c r="C172" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D172">
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:4">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B173">
         <v>46</v>
@@ -2573,7 +2587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:4">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>0</v>
       </c>
@@ -2587,9 +2601,9 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="175" spans="1:4">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B175">
         <v>46</v>
@@ -2601,9 +2615,9 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="176" spans="1:4">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B176">
         <v>46</v>
@@ -2612,7 +2626,7 @@
         <v>8</v>
       </c>
       <c r="D176">
-        <v>1.12237181892834</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
